--- a/medical_surveys_questionnaires/017_healthcare_climate_impact_awareness_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/017_healthcare_climate_impact_awareness_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare Climate Impact Awareness Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Survey Background</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This survey aims to understand the current state of climate change awareness and actions taken by healthcare staff.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -554,7 +558,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +593,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>action_items</t>
+          <t>climate_action_items</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -646,7 +650,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +662,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>climate_action_items</t>
+          <t>climate_action_items_essential</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Climate Action Items</t>
+          <t>Essential Climate Action Items</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +690,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Observed Impacts</t>
+          <t>Observed Impacts 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +713,105 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Staff Priorities</t>
+          <t>Staff Priorities 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>confidence_in_climate_action</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Confidence in Climate Action</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>progress_measurement</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Progress Measurement</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>confidence_level</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>confidence_scale</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Confidence Scale</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -730,12 +826,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -780,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -797,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>climate_change_mitigation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Climate Change Mitigation</t>
         </is>
       </c>
     </row>
@@ -814,80 +910,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>climate_change_adaptation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Climate Change Adaptation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>action_items_choices</t>
+          <t>staff_priorities_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>action_items_choices</t>
+          <t>climate_action_items_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>carbon_footprint_reduction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Carbon Footprint Reduction</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>expected_change_choices</t>
+          <t>climate_action_items_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sustainable_practices</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sustainable Practices</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>expected_change_choices</t>
+          <t>climate_action_items_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>energy_efficiency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Energy Efficiency</t>
         </is>
       </c>
     </row>
@@ -899,97 +995,301 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>climate_change_research</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Climate Change Research</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>climate_action_items_choices</t>
+          <t>expected_change_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>within_a_year</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Within a year</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>observed_impacts_2_choices</t>
+          <t>expected_change_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>within_2_years</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Within 2 years</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>observed_impacts_2_choices</t>
+          <t>expected_change_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>within_5_years</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Within 5 years</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>staff_priorities_2_choices</t>
+          <t>climate_action_items_essential_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>climate_change_policy_development</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Climate Change Policy Development</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>climate_action_items_essential_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>climate_change_training</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Climate Change Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>climate_action_items_essential_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>climate_change_research</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Climate Change Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>observed_impacts_2_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>observed_impacts_2_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>staff_priorities_2_choices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>climate_change_mitigation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Climate Change Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>staff_priorities_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>climate_change_adaptation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Climate Change Adaptation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>staff_priorities_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>progress_measurement_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>regular_reporting</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Regular Reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>progress_measurement_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>public_engagement</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Public Engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>progress_measurement_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>internal_review</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Internal Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>confidence_scale_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>confidence_scale_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>confidence_scale_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
